--- a/artfynd/A 65300-2021 artfynd.xlsx
+++ b/artfynd/A 65300-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 65300-2021 artfynd.xlsx
+++ b/artfynd/A 65300-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1029,6 +1029,142 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129248656</v>
+      </c>
+      <c r="B5" t="n">
+        <v>43982</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rönningen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>552520</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6628295</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Mats Jonsell</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Mats Jonsell</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 65300-2021 artfynd.xlsx
+++ b/artfynd/A 65300-2021 artfynd.xlsx
@@ -1034,7 +1034,7 @@
         <v>129248656</v>
       </c>
       <c r="B5" t="n">
-        <v>43985</v>
+        <v>43990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 65300-2021 artfynd.xlsx
+++ b/artfynd/A 65300-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4960474</v>
+        <v>308066</v>
       </c>
       <c r="B2" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rönningen, Vstm</t>
+          <t>(11G5b02), Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552432.8989602609</v>
+        <v>552462</v>
       </c>
       <c r="R2" t="n">
-        <v>6628164.977598282</v>
+        <v>6628203</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-07-13</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1995-07-13</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>110651021 / PHE FERF / Enstaka-sparsam (1)  / OBJ.AREA:0 ha</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,36 +761,30 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Lars Gullberg</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>4960475</v>
+        <v>650643</v>
       </c>
       <c r="B3" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222498</v>
+        <v>2667</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552566.8805319502</v>
+        <v>552567</v>
       </c>
       <c r="R3" t="n">
-        <v>6628248.429133285</v>
+        <v>6628248</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -865,21 +849,11 @@
           <t>2012-05-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2012-05-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -892,6 +866,11 @@
       <c r="AI3" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>på asp och block</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -909,15 +888,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>650643</v>
+        <v>71949378</v>
       </c>
       <c r="B4" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,37 +899,48 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2667</v>
+        <v>2869</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Rönningen, Vstm</t>
+          <t>Limes Norrlandicus, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552566.8805319502</v>
+        <v>552410</v>
       </c>
       <c r="R4" t="n">
-        <v>6628248.429133285</v>
+        <v>6628132</v>
       </c>
       <c r="S4" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +964,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2015-07-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1003,90 +978,70 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>på asp och block</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Caroline Greiser</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Caroline Greiser</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129248656</v>
+        <v>129722323</v>
       </c>
       <c r="B5" t="n">
-        <v>43990</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>101735</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rönningen, Vstm</t>
+          <t>Rönningen, Rönningen, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552520</v>
+        <v>552365</v>
       </c>
       <c r="R5" t="n">
-        <v>6628295</v>
+        <v>6628328</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,22 +1065,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i gott skick.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1134,36 +1084,377 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Per Appeltofft</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Appeltofft</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129248656</v>
+      </c>
+      <c r="B6" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rönningen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>552520</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6628295</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:18</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Mats Jonsell</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Mats Jonsell</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>4960474</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rönningen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>552433</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6628165</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2012-05-15</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2012-05-15</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>4960475</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rönningen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>552567</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6628248</v>
+      </c>
+      <c r="S8" t="n">
+        <v>50</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2012-05-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2012-05-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 65300-2021 artfynd.xlsx
+++ b/artfynd/A 65300-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,48 +675,51 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>308066</v>
+        <v>129190744</v>
       </c>
       <c r="B2" t="n">
-        <v>91909</v>
+        <v>80351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>392</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Aspgelélav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Collema subnigrescens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Degel.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>(11G5b02), Vstm</t>
+          <t>Knäppmora, Knäppmora, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>552462</v>
+        <v>552159</v>
       </c>
       <c r="R2" t="n">
-        <v>6628203</v>
+        <v>6628380</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,17 +743,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1995-07-13</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1995-07-13</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>110651021 / PHE FERF / Enstaka-sparsam (1)  / OBJ.AREA:0 ha</t>
+          <t>2025-10-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -759,70 +757,67 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Niklas Lönnell</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lars Gullberg</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Skogsstyrelsens naturvärdesobjekt</t>
-        </is>
-      </c>
+          <t>Per Appeltofft</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>650643</v>
+        <v>308066</v>
       </c>
       <c r="B3" t="n">
-        <v>96437</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2667</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alleniella complanata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Rönningen, Vstm</t>
+          <t>(11G5b02), Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>552567</v>
+        <v>552462</v>
       </c>
       <c r="R3" t="n">
-        <v>6628248</v>
+        <v>6628203</v>
       </c>
       <c r="S3" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -846,12 +841,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
+          <t>1995-07-13</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
+          <t>1995-07-13</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>110651021 / PHE FERF / Enstaka-sparsam (1)  / OBJ.AREA:0 ha</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -862,36 +862,30 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>på asp och block</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Niklas Lönnell</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Lars Gullberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Skogsstyrelsens naturvärdesobjekt</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>71949378</v>
+        <v>650643</v>
       </c>
       <c r="B4" t="n">
-        <v>97231</v>
+        <v>96437</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -899,48 +893,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2869</v>
+        <v>2667</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Girg.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Limes Norrlandicus, Vstm</t>
+          <t>Rönningen, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>552410</v>
+        <v>552567</v>
       </c>
       <c r="R4" t="n">
-        <v>6628132</v>
+        <v>6628248</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -964,12 +947,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2015-07-07</t>
+          <t>2012-05-15</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2015-07-07</t>
+          <t>2012-05-15</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -978,67 +961,84 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>på asp och block</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Caroline Greiser</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Caroline Greiser</t>
+          <t>Einar Marklund</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129722323</v>
+        <v>71949378</v>
       </c>
       <c r="B5" t="n">
-        <v>80432</v>
+        <v>97231</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Rönningen, Rönningen, Vstm</t>
+          <t>Limes Norrlandicus, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>552365</v>
+        <v>552410</v>
       </c>
       <c r="R5" t="n">
-        <v>6628328</v>
+        <v>6628132</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1065,17 +1065,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2015-07-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Riklig förekomst i gott skick.</t>
+          <t>2015-07-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,92 +1083,66 @@
       <c r="AG5" t="b">
         <v>0</v>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Per Appeltofft</t>
+          <t>Caroline Greiser</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Per Appeltofft</t>
+          <t>Caroline Greiser</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129248656</v>
+        <v>129722323</v>
       </c>
       <c r="B6" t="n">
-        <v>44177</v>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101735</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Rönningen, Vstm</t>
+          <t>Rönningen, Rönningen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>552520</v>
+        <v>552365</v>
       </c>
       <c r="R6" t="n">
-        <v>6628295</v>
+        <v>6628328</v>
       </c>
       <c r="S6" t="n">
-        <v>50</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1197,22 +1166,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2025-11-16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>16:18</t>
+          <t>2025-11-16</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Riklig förekomst i gott skick.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,43 +1185,44 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Mats Jonsell</t>
+          <t>Per Appeltofft</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>4960474</v>
+        <v>129248656</v>
       </c>
       <c r="B7" t="n">
-        <v>101326</v>
+        <v>44177</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,34 +1230,48 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>101735</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Rönningen, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>552433</v>
+        <v>552520</v>
       </c>
       <c r="R7" t="n">
-        <v>6628165</v>
+        <v>6628295</v>
       </c>
       <c r="S7" t="n">
         <v>50</v>
@@ -1319,12 +1298,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2012-05-15</t>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>16:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1336,27 +1325,37 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Mats Jonsell</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Einar Marklund</t>
+          <t>Mats Jonsell</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4960475</v>
+        <v>4960474</v>
       </c>
       <c r="B8" t="n">
         <v>101326</v>
@@ -1391,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>552567</v>
+        <v>552433</v>
       </c>
       <c r="R8" t="n">
-        <v>6628248</v>
+        <v>6628165</v>
       </c>
       <c r="S8" t="n">
         <v>50</v>
@@ -1455,6 +1454,108 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>4960475</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rönningen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>552567</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6628248</v>
+      </c>
+      <c r="S9" t="n">
+        <v>50</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Gunnilbo</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2012-05-15</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2012-05-15</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Einar Marklund</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
